--- a/backend/docs/tracker/IoT Water Filtration - Project Tracker.xlsx
+++ b/backend/docs/tracker/IoT Water Filtration - Project Tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Tracker" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Requirements" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks &amp; Issues" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Roles" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Project Tracker" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Client Requirements" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Risks &amp; Issues" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Team Roles" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Phase 2 — Backend API core implemented in TypeScript (auth, telemetry, alerts, test runs, calibration, lab validation, maintenance, settings, devices, users); telemetry ingestion, CSV export, and alert-generation logic remain. Frontend v1 complete; Phase 0 hardware gaps pending.</t>
+          <t>Phase 2 — Backend API core implemented in TypeScript (auth, telemetry, telemetry ingestion, alerts, test runs, calibration, lab validation, maintenance, settings, devices, users). CSV export and automatic alert-generation logic remain. Frontend v1 complete; Phase 0 hardware gaps pending.</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>• Backend API implemented (Express + TypeScript, commit 598f0e1) per API ROUTES PLAN — needs team review/approval; telemetry ingestion + CSV export + alert-generation logic still outstanding.</t>
+          <t>• Backend API implemented (Express + TypeScript, commit 46cd55f) per API ROUTES PLAN, including telemetry ingestion — needs team review/approval; CSV export + alert-generation logic still outstanding.</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>Generate fake pre/post pH, turbidity, TDS, temperature, flow and status payloads. backend/scripts/seedTestData.ts generates 5 simulated pre/post reading cycles per test run directly into sensor_readings (pH, turbidity, TDS, temperature, flow rate) for local testing — see docs/API_REFERENCE.md. This seeds the DB directly rather than acting as a live device posting over HTTP; a continuous HTTP-based simulator still depends on the ingestion endpoint in P2-02. Commit 598f0e1 on feature/backend-init.</t>
+          <t>Generate fake pre/post pH, turbidity, TDS, temperature, flow and status payloads. backend/scripts/seedTestData.ts seeds 5 simulated pre/post reading cycles directly into sensor_readings for local testing. backend/scripts/liveSimulator.ts (new) is the continuous version: it POSTs a reading batch to POST /devices/:id/readings every 5s (X-Device-Key auth), with per-parameter drift and occasional simulated unavailable readings, so dashboard live surfaces (SSE, SensorGrid) can be exercised the same way real hardware will drive them. Run via `npm run simulate`. See docs/API_REFERENCE.md.</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>Validate device ID, payload types, timestamps and missing fields; save telemetry. Implemented: POST /devices/:id/readings — batched ingestion, validates each reading's category/position/value against the device's registered sensors rows, skips (not fails) invalid/unregistered entries individually, and bumps devices.last_seen_at/connection_state as a heartbeat. Authenticated via a placeholder X-Device-Key shared secret, not the real device-auth decision (PENDING_DECISIONS §8). See docs/API_REFERENCE.md → Devices. Implemented on feature/backend-init (uncommitted as of this tracker update).</t>
+          <t>Validate device ID, payload types, timestamps and missing fields; save telemetry. Implemented: POST /devices/:id/readings — batched ingestion, validates each reading's category/position/value against the device's registered sensors rows, skips (not fails) invalid/unregistered entries individually, and bumps devices.last_seen_at/connection_state as a heartbeat. Authenticated via a placeholder X-Device-Key shared secret, not the real device-auth decision (PENDING_DECISIONS §8). See docs/API_REFERENCE.md → Devices. Committed on feature/backend-init (commit 46cd55f).</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">

--- a/backend/docs/tracker/IoT Water Filtration - Project Tracker.xlsx
+++ b/backend/docs/tracker/IoT Water Filtration - Project Tracker.xlsx
@@ -430,7 +430,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Phase 2 — Backend API core implemented in TypeScript (auth, telemetry, telemetry ingestion, alerts, test runs, calibration, lab validation, maintenance, settings, devices, users). CSV export and automatic alert-generation logic remain. Frontend v1 complete; Phase 0 hardware gaps pending.</t>
+          <t>Phase 2 — Backend API implemented in TypeScript: auth (+ Administrator-only account management), telemetry ingestion, automatic alert-generation (threshold/sensor-fault/device-offline), CSV export, data-retention purge job, and Row-Level Security on all tables. Frontend v1 complete; Phase 0 hardware gaps and full permissions-matrix decision still pending client/team input.</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>• Backend API implemented (Express + TypeScript, commit 46cd55f) per API ROUTES PLAN, including telemetry ingestion — needs team review/approval; CSV export + alert-generation logic still outstanding.</t>
+          <t>• Backend API implemented (Express + TypeScript) per API ROUTES PLAN, including telemetry ingestion, automatic alert-generation, CSV export, RLS, and data retention — needs team review/approval. Remaining gaps are all decision-blocked (approved thresholds, actuator control authority, full permissions matrix, device-auth mechanism) or need external infra (production Supabase project) — see backend/docs/tracker/todo.md.</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>Configure Supabase Auth and backend role checks. Supabase Auth wired end-to-end: POST /auth/login|logout|refresh|password-reset, GET /auth/me, PATCH /users/:id/role. profiles.role auto-provisioned via a DB trigger. Role-based authorization checks are NOT enforced yet — every authenticated user can call every route — pending a roles/permissions decision (docs/PENDING_DECISIONS.md §9). Commit 598f0e1.</t>
+          <t>Configure Supabase Auth and backend role checks. Supabase Auth wired end-to-end: POST /auth/login|logout|refresh|password-reset, GET /auth/me, PATCH /users/:id/role. profiles.role auto-provisioned via a DB trigger. requireRole(...) now gates the 4 account-management routes (POST /users, PATCH /:id/role, PATCH /:id/status, DELETE /:id) to Administrator — closes a self-escalation hole where any authenticated user could grant themselves Administrator. Every other route remains requireAuth-only: the full permissions matrix is still an open decision (docs/PENDING_DECISIONS.md 'user authorization'). Commit 7ba92c0.</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>Support sensor, offline, no-flow, pump, UV-C, filter and water-quality alert categories. Storage/API implemented: alerts table (+source/title/message), GET /alerts, GET /alerts/:id, PATCH acknowledge/resolve, GET /alerts/stream (SSE), alert_state_changes audit trail. No automatic alert-GENERATION logic yet — nothing evaluates sensor readings/device faults into alert rows — blocked on P0-06 thresholds and P0-05 control-authority decisions. Commit 598f0e1.</t>
+          <t>Support sensor, offline, no-flow, pump, UV-C, filter and water-quality alert categories. Storage/API implemented: alerts table (+source/title/message), GET /alerts, GET /alerts/:id, PATCH acknowledge/resolve, GET /alerts/stream (SSE), alert_state_changes audit trail. Alert-GENERATION now implemented for what isn't blocked: src/lib/alertEngine.ts evaluates every ingested reading for threshold breaches (reads the thresholds table — inert until one is configured, since approved values are still TBD) and sensor faults (unavailable/invalid readings); src/lib/deviceWatchdog.ts separately flags devices gone quiet as Offline and auto-resolves the alert when the device reports again. Both dedupe per device+source. Still blocked: pump/UV-C/filter alert categories — no such telemetry exists yet, and P0-05 (control authority) remains open. Commit 8ab89e1.</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>Export telemetry, test runs and comparison data with date filters. Not started. Candidate endpoint: GET /export/csv per docs/API_ROUTES_DRAFT.md §8; column set/order still TBD (PENDING_DECISIONS §12). Tracked in docs/tracker/todo.md.</t>
+          <t>Export telemetry, test runs and comparison data with date filters. Implemented: GET /export/csv?type=telemetry|test-runs|alerts|laboratory-validation (src/routes/export.routes.ts), filters mirror the equivalent JSON routes, capped at 5000 rows. Column set/order is explicitly documented as a placeholder, not a final contract — docs/PENDING_DECISIONS.md still lists 'CSV column order' as open. Commit e629d6d.</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
